--- a/imsbackend/refe/products.xlsx
+++ b/imsbackend/refe/products.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
   <si>
     <t>businessId</t>
   </si>
@@ -66,10 +66,19 @@
     <t>barcode</t>
   </si>
   <si>
-    <t>hell</t>
-  </si>
-  <si>
     <t>h1h1h1</t>
+  </si>
+  <si>
+    <t>Laptop</t>
+  </si>
+  <si>
+    <t>Pen</t>
+  </si>
+  <si>
+    <t>lap</t>
+  </si>
+  <si>
+    <t>pen</t>
   </si>
 </sst>
 </file>
@@ -425,7 +434,7 @@
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.90625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.81640625" style="1" customWidth="1"/>
     <col min="3" max="3" width="4" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.36328125" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.26953125" style="1" bestFit="1" customWidth="1"/>
@@ -489,14 +498,14 @@
       <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="2">
-        <v>1</v>
+      <c r="B2" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>16</v>
       </c>
       <c r="E2" s="2">
         <v>9435562511</v>
@@ -530,14 +539,14 @@
       <c r="A3" s="2">
         <v>1</v>
       </c>
-      <c r="B3" s="2">
-        <v>1</v>
+      <c r="B3" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>16</v>
       </c>
       <c r="E3" s="2">
         <v>9435562511</v>
